--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-19) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-19) Legacy.xlsx
@@ -897,19 +897,19 @@
         <v>105032048100</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>104658066643</v>
+        <v>104659374334</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>35000000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>104693066643</v>
+        <v>104694374334</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-338981457</v>
+        <v>-337673766</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>99.67725902414351</v>
+        <v>99.6785040641324</v>
       </c>
     </row>
     <row r="17">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-19) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-19) Legacy.xlsx
@@ -897,19 +897,19 @@
         <v>105032048100</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>104659374334</v>
+        <v>104658066643</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>35000000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>104694374334</v>
+        <v>104693066643</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-337673766</v>
+        <v>-338981457</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>99.6785040641324</v>
+        <v>99.67725902414351</v>
       </c>
     </row>
     <row r="17">
